--- a/data/nzd0142/nzd0142.xlsx
+++ b/data/nzd0142/nzd0142.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G327"/>
+  <dimension ref="A1:G330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9265,6 +9265,87 @@
         <v>369.17</v>
       </c>
       <c r="G327" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>356.51</v>
+      </c>
+      <c r="C328" t="n">
+        <v>359.81</v>
+      </c>
+      <c r="D328" t="n">
+        <v>355.33</v>
+      </c>
+      <c r="E328" t="n">
+        <v>356.39</v>
+      </c>
+      <c r="F328" t="n">
+        <v>370.14</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>357.44</v>
+      </c>
+      <c r="C329" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="D329" t="n">
+        <v>355.98</v>
+      </c>
+      <c r="E329" t="n">
+        <v>357.03</v>
+      </c>
+      <c r="F329" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>357.73</v>
+      </c>
+      <c r="C330" t="n">
+        <v>360.47</v>
+      </c>
+      <c r="D330" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="E330" t="n">
+        <v>357.14</v>
+      </c>
+      <c r="F330" t="n">
+        <v>370.48</v>
+      </c>
+      <c r="G330" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9281,7 +9362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B345"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12734,6 +12815,46 @@
       </c>
       <c r="B345" t="n">
         <v>-0.72</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -12902,28 +13023,28 @@
         <v>0.0985</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09962697837262367</v>
+        <v>0.08833039747478932</v>
       </c>
       <c r="J2" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03726487741759543</v>
+        <v>0.02932151575433484</v>
       </c>
       <c r="M2" t="n">
-        <v>2.996908336059077</v>
+        <v>3.02702376747405</v>
       </c>
       <c r="N2" t="n">
-        <v>14.23592458381079</v>
+        <v>14.48144664900181</v>
       </c>
       <c r="O2" t="n">
-        <v>3.773052422616307</v>
+        <v>3.805449598799308</v>
       </c>
       <c r="P2" t="n">
-        <v>361.047218137463</v>
+        <v>361.1691884291324</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12980,28 +13101,28 @@
         <v>0.129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1090571258218918</v>
+        <v>0.09639757429321515</v>
       </c>
       <c r="J3" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K3" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0250791112026798</v>
+        <v>0.01971691126246689</v>
       </c>
       <c r="M3" t="n">
-        <v>4.14877331362557</v>
+        <v>4.167373444308816</v>
       </c>
       <c r="N3" t="n">
-        <v>25.6678783530922</v>
+        <v>25.90284298074213</v>
       </c>
       <c r="O3" t="n">
-        <v>5.066347634449516</v>
+        <v>5.089483567194429</v>
       </c>
       <c r="P3" t="n">
-        <v>364.5785583838597</v>
+        <v>364.7152491981482</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13058,28 +13179,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2590634235191374</v>
+        <v>0.2406922298548438</v>
       </c>
       <c r="J4" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1060428560462537</v>
+        <v>0.09185654191171699</v>
       </c>
       <c r="M4" t="n">
-        <v>4.49581974856055</v>
+        <v>4.543000583318642</v>
       </c>
       <c r="N4" t="n">
-        <v>31.41030304044813</v>
+        <v>32.11227696573726</v>
       </c>
       <c r="O4" t="n">
-        <v>5.60448954325442</v>
+        <v>5.666769535258802</v>
       </c>
       <c r="P4" t="n">
-        <v>359.5752910739808</v>
+        <v>359.773651284873</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13136,28 +13257,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2966094356385645</v>
+        <v>0.2786599819148328</v>
       </c>
       <c r="J5" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K5" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1015587474082016</v>
+        <v>0.09049299967924673</v>
       </c>
       <c r="M5" t="n">
-        <v>5.371745584721722</v>
+        <v>5.401920044945058</v>
       </c>
       <c r="N5" t="n">
-        <v>43.20827379210377</v>
+        <v>43.75652895969196</v>
       </c>
       <c r="O5" t="n">
-        <v>6.573300068618789</v>
+        <v>6.614871802211435</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2268344859313</v>
+        <v>359.4206438814825</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13214,28 +13335,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06091961342883879</v>
+        <v>-0.06212840162882436</v>
       </c>
       <c r="J6" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K6" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008625361342653792</v>
+        <v>0.009136708106113778</v>
       </c>
       <c r="M6" t="n">
-        <v>3.923603024425228</v>
+        <v>3.894162301439106</v>
       </c>
       <c r="N6" t="n">
-        <v>23.6809666641799</v>
+        <v>23.46966785289418</v>
       </c>
       <c r="O6" t="n">
-        <v>4.866309347357595</v>
+        <v>4.844550325148267</v>
       </c>
       <c r="P6" t="n">
-        <v>372.7387053106812</v>
+        <v>372.7517554040922</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13273,7 +13394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G327"/>
+  <dimension ref="A1:G330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25375,6 +25496,117 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-36.61355094150487,175.56490825636698</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-36.61414021218592,175.5654287725147</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-36.61455698619019,175.56616984833695</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-36.61481949976057,175.56701079903053</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-36.614823372299654,175.56791875537857</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-36.61354625856304,175.56491687455033</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-36.614136352118656,175.56543330543622</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-36.614551718588764,175.56617302174416</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-36.61481393067571,175.56701265164165</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-36.614819101663265,175.56791959859058</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-36.613544798290725,175.5649195619406</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-36.61413589414457,175.56543384324047</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-36.61454693722741,175.5661759022211</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-36.61481297348926,175.56701297005915</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-36.61482034726554,175.56791935265375</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0142/nzd0142.xlsx
+++ b/data/nzd0142/nzd0142.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G330"/>
+  <dimension ref="A1:G331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9348,6 +9348,33 @@
       <c r="G330" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>359.07</v>
+      </c>
+      <c r="C331" t="n">
+        <v>361.71</v>
+      </c>
+      <c r="D331" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="E331" t="n">
+        <v>357.83</v>
+      </c>
+      <c r="F331" t="n">
+        <v>371.07</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12855,6 +12882,16 @@
       </c>
       <c r="B349" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -13023,28 +13060,28 @@
         <v>0.0985</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08833039747478932</v>
+        <v>0.08574955031896393</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02932151575433484</v>
+        <v>0.02773615504221738</v>
       </c>
       <c r="M2" t="n">
-        <v>3.02702376747405</v>
+        <v>3.031470153238997</v>
       </c>
       <c r="N2" t="n">
-        <v>14.48144664900181</v>
+        <v>14.49748911654522</v>
       </c>
       <c r="O2" t="n">
-        <v>3.805449598799308</v>
+        <v>3.807556843508082</v>
       </c>
       <c r="P2" t="n">
-        <v>361.1691884291324</v>
+        <v>361.1971108371142</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13101,28 +13138,28 @@
         <v>0.129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09639757429321515</v>
+        <v>0.09316759162232427</v>
       </c>
       <c r="J3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01971691126246689</v>
+        <v>0.01848890268462833</v>
       </c>
       <c r="M3" t="n">
-        <v>4.167373444308816</v>
+        <v>4.169178389944088</v>
       </c>
       <c r="N3" t="n">
-        <v>25.90284298074213</v>
+        <v>25.91821123303518</v>
       </c>
       <c r="O3" t="n">
-        <v>5.089483567194429</v>
+        <v>5.090993148005129</v>
       </c>
       <c r="P3" t="n">
-        <v>364.7152491981482</v>
+        <v>364.7501946592566</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13179,28 +13216,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2406922298548438</v>
+        <v>0.235709775664808</v>
       </c>
       <c r="J4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09185654191171699</v>
+        <v>0.08836774948170423</v>
       </c>
       <c r="M4" t="n">
-        <v>4.543000583318642</v>
+        <v>4.553209156595729</v>
       </c>
       <c r="N4" t="n">
-        <v>32.11227696573726</v>
+        <v>32.23831126358171</v>
       </c>
       <c r="O4" t="n">
-        <v>5.666769535258802</v>
+        <v>5.677879116675673</v>
       </c>
       <c r="P4" t="n">
-        <v>359.773651284873</v>
+        <v>359.8275568865009</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13257,28 +13294,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2786599819148328</v>
+        <v>0.2734316800810242</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09049299967924673</v>
+        <v>0.08747195279295172</v>
       </c>
       <c r="M5" t="n">
-        <v>5.401920044945058</v>
+        <v>5.40866409638664</v>
       </c>
       <c r="N5" t="n">
-        <v>43.75652895969196</v>
+        <v>43.8698622272892</v>
       </c>
       <c r="O5" t="n">
-        <v>6.614871802211435</v>
+        <v>6.6234328129218</v>
       </c>
       <c r="P5" t="n">
-        <v>359.4206438814825</v>
+        <v>359.4772093299732</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13335,28 +13372,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06212840162882436</v>
+        <v>-0.06214044452491043</v>
       </c>
       <c r="J6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009136708106113778</v>
+        <v>0.009196834685874844</v>
       </c>
       <c r="M6" t="n">
-        <v>3.894162301439106</v>
+        <v>3.882424692278404</v>
       </c>
       <c r="N6" t="n">
-        <v>23.46966785289418</v>
+        <v>23.39854895209748</v>
       </c>
       <c r="O6" t="n">
-        <v>4.844550325148267</v>
+        <v>4.837204663036027</v>
       </c>
       <c r="P6" t="n">
-        <v>372.7517554040922</v>
+        <v>372.7518856972236</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13394,7 +13431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G330"/>
+  <dimension ref="A1:G331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25607,6 +25644,43 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-36.61353805082486,175.56493197953577</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-36.61412778146026,175.56544337005698</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-36.6145385901049,175.5661809308495</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-36.61480696931961,175.5670149674052</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-36.61481509794164,175.56792038910174</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
